--- a/_stats_outputs/erosion_totals.xlsx
+++ b/_stats_outputs/erosion_totals.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O13"/>
+  <dimension ref="A1:P13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -362,70 +362,75 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>dt</t>
+          <t>t</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>type</t>
+          <t>slope_pos</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>estimate</t>
+          <t>forest_est</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>std_error</t>
+          <t>forest_err</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>p_value</t>
+          <t>forest_pval</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>bsfs_pval</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>estimate_mm</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>std_error_mm</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>worms</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>bd_mean</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>bd_se</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>tons_km2</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>tons_km2_se</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>tons_acre</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>tons_acre_se</t>
         </is>
@@ -438,50 +443,53 @@
         </is>
       </c>
       <c r="B2">
-        <v>73</v>
+        <v>2.398160315374507</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>bs</t>
+          <t>BS</t>
         </is>
       </c>
       <c r="D2">
-        <v>-2.972203031966552</v>
+        <v>-3.346878856369181</v>
       </c>
       <c r="E2">
-        <v>0.3580150973593705</v>
+        <v>0.6721129136707557</v>
       </c>
       <c r="F2">
-        <v>1.199350371471111E-14</v>
+        <v>0.007599082179277888</v>
       </c>
       <c r="G2">
-        <v>-7.137198070182841</v>
+        <v>0.2363310793492502</v>
       </c>
       <c r="H2">
-        <v>0.8597073061590147</v>
-      </c>
-      <c r="I2" t="inlineStr">
+        <v>-8.026352053710584</v>
+      </c>
+      <c r="I2">
+        <v>1.611834517015938</v>
+      </c>
+      <c r="J2" t="inlineStr">
         <is>
           <t>EW</t>
         </is>
       </c>
-      <c r="J2">
+      <c r="K2">
         <v>0.9102823215800314</v>
       </c>
-      <c r="K2">
+      <c r="L2">
         <v>0.005410543260007655</v>
       </c>
-      <c r="L2">
-        <v>-6496.865228902557</v>
-      </c>
       <c r="M2">
-        <v>783.5285367044784</v>
+        <v>-7306.246381270323</v>
       </c>
       <c r="N2">
-        <v>-25.87669305089941</v>
+        <v>1467.867000750013</v>
       </c>
       <c r="O2">
-        <v>3.120755429976344</v>
+        <v>-29.10041817110508</v>
+      </c>
+      <c r="P2">
+        <v>5.846441703758192</v>
       </c>
     </row>
     <row r="3">
@@ -491,580 +499,595 @@
         </is>
       </c>
       <c r="B3">
-        <v>73</v>
+        <v>2.398160315374507</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>fs</t>
+          <t>FS</t>
         </is>
       </c>
       <c r="D3">
-        <v>0.5497091268668365</v>
+        <v>-2.023785803793768</v>
       </c>
       <c r="E3">
-        <v>0.5063098062199471</v>
+        <v>0.6721129136707557</v>
       </c>
       <c r="F3">
-        <v>0.2023586365478415</v>
-      </c>
-      <c r="G3">
-        <v>1.320025205963127</v>
+        <v>0.03950779448759779</v>
       </c>
       <c r="H3">
-        <v>1.215809732041321</v>
-      </c>
-      <c r="I3" t="inlineStr">
+        <v>-4.853362801476512</v>
+      </c>
+      <c r="I3">
+        <v>1.611834517015938</v>
+      </c>
+      <c r="J3" t="inlineStr">
         <is>
           <t>EW</t>
         </is>
       </c>
-      <c r="J3">
+      <c r="K3">
         <v>0.9102823215800314</v>
       </c>
-      <c r="K3">
+      <c r="L3">
         <v>0.005410543260007655</v>
       </c>
-      <c r="L3">
-        <v>1201.595609028274</v>
-      </c>
       <c r="M3">
-        <v>1106.753150123595</v>
+        <v>-4417.930358398205</v>
       </c>
       <c r="N3">
-        <v>4.785895912971776</v>
+        <v>1467.459432643888</v>
       </c>
       <c r="O3">
-        <v>4.408143087447414</v>
+        <v>-17.59639822847786</v>
+      </c>
+      <c r="P3">
+        <v>5.844818380138578</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>WD</t>
+          <t>LRE</t>
         </is>
       </c>
       <c r="B4">
-        <v>73</v>
+        <v>2.529566360052562</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>bs</t>
+          <t>BS</t>
         </is>
       </c>
       <c r="D4">
-        <v>-1.054667005822169</v>
+        <v>-2.652248957106386</v>
       </c>
       <c r="E4">
-        <v>0.6897618556613508</v>
+        <v>0.6439708931541994</v>
       </c>
       <c r="F4">
-        <v>0.1277475365557665</v>
+        <v>0.01462924584275813</v>
       </c>
       <c r="G4">
-        <v>-2.532588533717708</v>
+        <v>0.7201742245241556</v>
       </c>
       <c r="H4">
-        <v>1.65633603497627</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>JW</t>
-        </is>
-      </c>
-      <c r="J4">
-        <v>0.6192681449169999</v>
+        <v>-6.709039740380804</v>
+      </c>
+      <c r="I4">
+        <v>1.628967108175865</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>EW</t>
+        </is>
       </c>
       <c r="K4">
-        <v>0.008516172438153556</v>
+        <v>0.9102823215800314</v>
       </c>
       <c r="L4">
-        <v>-1568.35140311343</v>
+        <v>0.005410543260007655</v>
       </c>
       <c r="M4">
-        <v>1025.942875824013</v>
+        <v>-6107.12027044653</v>
       </c>
       <c r="N4">
-        <v>-6.246666111183745</v>
+        <v>1483.264202384465</v>
       </c>
       <c r="O4">
-        <v>4.086279759560206</v>
+        <v>-24.32435814740846</v>
+      </c>
+      <c r="P4">
+        <v>5.907767996747161</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>WD</t>
+          <t>LRE</t>
         </is>
       </c>
       <c r="B5">
-        <v>73</v>
+        <v>2.529566360052562</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>fs</t>
+          <t>FS</t>
         </is>
       </c>
       <c r="D5">
-        <v>-0.2919915069809507</v>
+        <v>-2.302078531932976</v>
       </c>
       <c r="E5">
-        <v>0.9754705710839164</v>
+        <v>0.6439708931541994</v>
       </c>
       <c r="F5">
-        <v>0.7922144381015715</v>
-      </c>
-      <c r="G5">
-        <v>-0.7011638161055723</v>
+        <v>0.02327515101231295</v>
       </c>
       <c r="H5">
-        <v>2.342412884510721</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>JW</t>
-        </is>
-      </c>
-      <c r="J5">
-        <v>0.6192681449169999</v>
+        <v>-5.823260412576844</v>
+      </c>
+      <c r="I5">
+        <v>1.628967108175865</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>EW</t>
+        </is>
       </c>
       <c r="K5">
-        <v>0.008516172438153556</v>
+        <v>0.9102823215800314</v>
       </c>
       <c r="L5">
-        <v>-434.2084156826222</v>
+        <v>0.005410543260007655</v>
       </c>
       <c r="M5">
-        <v>1450.593971676612</v>
+        <v>-5300.811007525541</v>
       </c>
       <c r="N5">
-        <v>-1.729430655687852</v>
+        <v>1483.154654094453</v>
       </c>
       <c r="O5">
-        <v>5.777644082806592</v>
+        <v>-21.11286821101835</v>
+      </c>
+      <c r="P5">
+        <v>5.907331671323282</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MAG</t>
+          <t>LRJ</t>
         </is>
       </c>
       <c r="B6">
-        <v>70</v>
+        <v>2.266754270696452</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>bs</t>
+          <t>BS</t>
         </is>
       </c>
       <c r="D6">
-        <v>-3.704461401319306</v>
+        <v>-2.590352932464441</v>
       </c>
       <c r="E6">
-        <v>1.049240775682377</v>
+        <v>0.6575253010120951</v>
       </c>
       <c r="F6">
-        <v>0.0005085328977981283</v>
+        <v>0.01696578943374394</v>
       </c>
       <c r="G6">
-        <v>-8.530009805669456</v>
+        <v>0.5623225497890948</v>
       </c>
       <c r="H6">
-        <v>2.416014944005473</v>
-      </c>
-      <c r="I6" t="inlineStr">
+        <v>-5.87169357227485</v>
+      </c>
+      <c r="I6">
+        <v>1.490448284160137</v>
+      </c>
+      <c r="J6" t="inlineStr">
         <is>
           <t>JW</t>
         </is>
       </c>
-      <c r="J6">
+      <c r="K6">
         <v>0.6192681449169999</v>
       </c>
-      <c r="K6">
+      <c r="L6">
         <v>0.008516172438153556</v>
       </c>
-      <c r="L6">
-        <v>-5282.363348480743</v>
-      </c>
       <c r="M6">
-        <v>1497.923571166621</v>
+        <v>-3636.152786023719</v>
       </c>
       <c r="N6">
-        <v>-21.03939209695549</v>
+        <v>924.3406858695798</v>
       </c>
       <c r="O6">
-        <v>5.966155537958304</v>
+        <v>-14.48261680287346</v>
+      </c>
+      <c r="P6">
+        <v>3.681603259414587</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MAG</t>
+          <t>LRJ</t>
         </is>
       </c>
       <c r="B7">
-        <v>70</v>
+        <v>2.266754270696452</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>fs</t>
+          <t>FS</t>
         </is>
       </c>
       <c r="D7">
-        <v>1.573218527762946</v>
+        <v>-2.0036360584518</v>
       </c>
       <c r="E7">
-        <v>1.483850535164893</v>
+        <v>0.6575253010120951</v>
       </c>
       <c r="F7">
-        <v>0.2545973202353868</v>
-      </c>
-      <c r="G7">
-        <v>3.622542662612047</v>
+        <v>0.03813044306717106</v>
       </c>
       <c r="H7">
-        <v>3.416761100708636</v>
-      </c>
-      <c r="I7" t="inlineStr">
+        <v>-4.541750592417023</v>
+      </c>
+      <c r="I7">
+        <v>1.490448284160137</v>
+      </c>
+      <c r="J7" t="inlineStr">
         <is>
           <t>JW</t>
         </is>
       </c>
-      <c r="J7">
+      <c r="K7">
         <v>0.6192681449169999</v>
       </c>
-      <c r="K7">
+      <c r="L7">
         <v>0.008516172438153556</v>
       </c>
-      <c r="L7">
-        <v>2243.325274558452</v>
-      </c>
       <c r="M7">
-        <v>2116.116198117118</v>
+        <v>-2812.561464041775</v>
       </c>
       <c r="N7">
-        <v>8.935053675552297</v>
+        <v>923.7972079109103</v>
       </c>
       <c r="O7">
-        <v>8.428386212339914</v>
+        <v>-11.2022932795377</v>
+      </c>
+      <c r="P7">
+        <v>3.679438613570641</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>LRE</t>
+          <t>LRW</t>
         </is>
       </c>
       <c r="B8">
-        <v>77</v>
+        <v>2.529566360052562</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>bs</t>
+          <t>BS</t>
         </is>
       </c>
       <c r="D8">
-        <v>-3.685901184817794</v>
+        <v>-2.309121715907596</v>
       </c>
       <c r="E8">
-        <v>0.5220469905099397</v>
+        <v>0.574885038347449</v>
       </c>
       <c r="F8">
-        <v>2.334409443926573E-11</v>
+        <v>0.0003087071503610556</v>
       </c>
       <c r="G8">
-        <v>-9.335999711545071</v>
+        <v>0.2490888123193706</v>
       </c>
       <c r="H8">
-        <v>1.322290074646887</v>
-      </c>
-      <c r="I8" t="inlineStr">
+        <v>-5.841076613826704</v>
+      </c>
+      <c r="I8">
+        <v>1.454209853901234</v>
+      </c>
+      <c r="J8" t="inlineStr">
         <is>
           <t>EW</t>
         </is>
       </c>
-      <c r="J8">
+      <c r="K8">
         <v>0.9102823215800314</v>
       </c>
-      <c r="K8">
+      <c r="L8">
         <v>0.005410543260007655</v>
       </c>
-      <c r="L8">
-        <v>-8498.39549169575</v>
-      </c>
       <c r="M8">
-        <v>1204.716726537844</v>
+        <v>-5317.028780561001</v>
       </c>
       <c r="N8">
-        <v>-33.84868914710508</v>
+        <v>1324.118722577073</v>
       </c>
       <c r="O8">
-        <v>4.798327169727978</v>
+        <v>-21.1774627993347</v>
+      </c>
+      <c r="P8">
+        <v>5.273899417621713</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>LRE</t>
+          <t>LRW</t>
         </is>
       </c>
       <c r="B9">
-        <v>77</v>
+        <v>2.529566360052562</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>fs</t>
+          <t>FS</t>
         </is>
       </c>
       <c r="D9">
-        <v>0.3546779250189292</v>
+        <v>-3.262494319297206</v>
       </c>
       <c r="E9">
-        <v>0.7382859341752143</v>
+        <v>0.574885038347449</v>
       </c>
       <c r="F9">
-        <v>0.5198609087920016</v>
-      </c>
-      <c r="G9">
-        <v>0.8983618495545247</v>
+        <v>2.277256934190319E-06</v>
       </c>
       <c r="H9">
-        <v>1.870000556956957</v>
-      </c>
-      <c r="I9" t="inlineStr">
+        <v>-8.252695879956793</v>
+      </c>
+      <c r="I9">
+        <v>1.454209853901234</v>
+      </c>
+      <c r="J9" t="inlineStr">
         <is>
           <t>EW</t>
         </is>
       </c>
-      <c r="J9">
+      <c r="K9">
         <v>0.9102823215800314</v>
       </c>
-      <c r="K9">
+      <c r="L9">
         <v>0.005410543260007655</v>
       </c>
-      <c r="L9">
-        <v>817.7629100314236</v>
-      </c>
       <c r="M9">
-        <v>1702.235387961668</v>
+        <v>-7512.28316490103</v>
       </c>
       <c r="N9">
-        <v>3.25710924664939</v>
+        <v>1324.494386271162</v>
       </c>
       <c r="O9">
-        <v>6.779919404623906</v>
+        <v>-29.92105249540782</v>
+      </c>
+      <c r="P9">
+        <v>5.2753956675453</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LRW</t>
+          <t>MAG</t>
         </is>
       </c>
       <c r="B10">
-        <v>77</v>
+        <v>2.299605781865966</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>bs</t>
+          <t>BS</t>
         </is>
       </c>
       <c r="D10">
-        <v>-1.962696597093065</v>
+        <v>-3.209547199264947</v>
       </c>
       <c r="E10">
-        <v>0.4877951197862384</v>
+        <v>3.051674051339206</v>
       </c>
       <c r="F10">
-        <v>7.973704403488446E-05</v>
+        <v>0.3522607045418362</v>
       </c>
       <c r="G10">
-        <v>-4.971303880794934</v>
+        <v>0.8539754684526759</v>
       </c>
       <c r="H10">
-        <v>1.235533691563828</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>EW</t>
-        </is>
-      </c>
-      <c r="J10">
-        <v>0.9102823215800314</v>
+        <v>-7.38069329660139</v>
+      </c>
+      <c r="I10">
+        <v>7.017647292829975</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>JW</t>
+        </is>
       </c>
       <c r="K10">
-        <v>0.005410543260007655</v>
+        <v>0.6192681449169999</v>
       </c>
       <c r="L10">
-        <v>-4525.290037889832</v>
+        <v>0.008516172438153556</v>
       </c>
       <c r="M10">
-        <v>1125.006064963748</v>
+        <v>-4570.628245987679</v>
       </c>
       <c r="N10">
-        <v>-18.02400652484344</v>
+        <v>4346.259948278062</v>
       </c>
       <c r="O10">
-        <v>4.480843544969853</v>
+        <v>-18.20458636651948</v>
+      </c>
+      <c r="P10">
+        <v>17.31093852781169</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>LRW</t>
+          <t>MAG</t>
         </is>
       </c>
       <c r="B11">
-        <v>77</v>
+        <v>2.299605781865966</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>fs</t>
+          <t>FS</t>
         </is>
       </c>
       <c r="D11">
-        <v>-0.8717593984638676</v>
+        <v>-2.362550965254707</v>
       </c>
       <c r="E11">
-        <v>0.6898464740611059</v>
+        <v>3.051674051339206</v>
       </c>
       <c r="F11">
-        <v>0.243269994461641</v>
-      </c>
-      <c r="G11">
-        <v>-2.20807479216177</v>
+        <v>0.4820366224397812</v>
       </c>
       <c r="H11">
-        <v>1.747308503378459</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>EW</t>
-        </is>
-      </c>
-      <c r="J11">
-        <v>0.9102823215800314</v>
+        <v>-5.432935859652742</v>
+      </c>
+      <c r="I11">
+        <v>7.017647292829975</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>JW</t>
+        </is>
       </c>
       <c r="K11">
-        <v>0.005410543260007655</v>
+        <v>0.6192681449169999</v>
       </c>
       <c r="L11">
-        <v>-2009.971448031362</v>
+        <v>0.008516172438153556</v>
       </c>
       <c r="M11">
-        <v>1590.58890801893</v>
+        <v>-3364.4441112602</v>
       </c>
       <c r="N11">
-        <v>-8.00561691974101</v>
+        <v>4346.051709970288</v>
       </c>
       <c r="O11">
-        <v>6.335236993968504</v>
+        <v>-13.40041458250973</v>
+      </c>
+      <c r="P11">
+        <v>17.31010912492555</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LRJ</t>
+          <t>WD</t>
         </is>
       </c>
       <c r="B12">
-        <v>69</v>
+        <v>2.398160315374507</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>bs</t>
+          <t>BS</t>
         </is>
       </c>
       <c r="D12">
-        <v>-3.513983734987653</v>
+        <v>-2.015240253276509</v>
       </c>
       <c r="E12">
-        <v>0.5045130976286406</v>
+        <v>0.8848316662159894</v>
       </c>
       <c r="F12">
-        <v>4.060148226100291E-11</v>
+        <v>0.02916216361765942</v>
       </c>
       <c r="G12">
-        <v>-7.975818345860135</v>
+        <v>0.8166337376052223</v>
       </c>
       <c r="H12">
-        <v>1.145111965012375</v>
-      </c>
-      <c r="I12" t="inlineStr">
+        <v>-4.832869201352993</v>
+      </c>
+      <c r="I12">
+        <v>2.121968187705888</v>
+      </c>
+      <c r="J12" t="inlineStr">
         <is>
           <t>JW</t>
         </is>
       </c>
-      <c r="J12">
+      <c r="K12">
         <v>0.6192681449169999</v>
       </c>
-      <c r="K12">
+      <c r="L12">
         <v>0.008516172438153556</v>
       </c>
-      <c r="L12">
-        <v>-4939.17023123578</v>
-      </c>
       <c r="M12">
-        <v>712.3769250094695</v>
+        <v>-2992.841944948371</v>
       </c>
       <c r="N12">
-        <v>-19.6724708758377</v>
+        <v>1314.711687399592</v>
       </c>
       <c r="O12">
-        <v>2.837362077792012</v>
+        <v>-11.92034152328687</v>
+      </c>
+      <c r="P12">
+        <v>5.23643166152239</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LRJ</t>
+          <t>WD</t>
         </is>
       </c>
       <c r="B13">
-        <v>69</v>
+        <v>2.398160315374507</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>fs</t>
+          <t>FS</t>
         </is>
       </c>
       <c r="D13">
-        <v>0.2414075946472465</v>
+        <v>-1.722825294015962</v>
       </c>
       <c r="E13">
-        <v>0.7134892650612854</v>
+        <v>0.8848316662159894</v>
       </c>
       <c r="F13">
-        <v>0.6173429156469129</v>
-      </c>
-      <c r="G13">
-        <v>0.5479317115348686</v>
+        <v>0.05982545801930361</v>
       </c>
       <c r="H13">
-        <v>1.619432871356207</v>
-      </c>
-      <c r="I13" t="inlineStr">
+        <v>-4.131611250432497</v>
+      </c>
+      <c r="I13">
+        <v>2.121968187705888</v>
+      </c>
+      <c r="J13" t="inlineStr">
         <is>
           <t>JW</t>
         </is>
       </c>
-      <c r="J13">
+      <c r="K13">
         <v>0.6192681449169999</v>
       </c>
-      <c r="K13">
+      <c r="L13">
         <v>0.008516172438153556</v>
       </c>
-      <c r="L13">
-        <v>339.3166545433948</v>
-      </c>
       <c r="M13">
-        <v>1002.874046009707</v>
+        <v>-2558.575234573539</v>
       </c>
       <c r="N13">
-        <v>1.351481461800413</v>
+        <v>1314.538283069393</v>
       </c>
       <c r="O13">
-        <v>3.994397750758081</v>
+        <v>-10.19067868272159</v>
+      </c>
+      <c r="P13">
+        <v>5.235741000647006</v>
       </c>
     </row>
   </sheetData>

--- a/_stats_outputs/erosion_totals.xlsx
+++ b/_stats_outputs/erosion_totals.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P13"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -362,77 +362,27 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>t</t>
+          <t>slope_pos</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>slope_pos</t>
+          <t>estimate_mm</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>forest_est</t>
+          <t>std_error_mm</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>forest_err</t>
+          <t>tons_km2</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>forest_pval</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>bsfs_pval</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>estimate_mm</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>std_error_mm</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>worms</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>bd_mean</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>bd_se</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>tons_km2</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
           <t>tons_km2_se</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>tons_acre</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>tons_acre_se</t>
         </is>
       </c>
     </row>
@@ -442,54 +392,22 @@
           <t>ASH</t>
         </is>
       </c>
-      <c r="B2">
-        <v>2.398160315374507</v>
-      </c>
-      <c r="C2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>BS</t>
         </is>
       </c>
+      <c r="C2">
+        <v>-8.026352053710584</v>
+      </c>
       <c r="D2">
-        <v>-3.346878856369181</v>
+        <v>1.611834517015938</v>
       </c>
       <c r="E2">
-        <v>0.6721129136707557</v>
+        <v>-7306.246381270323</v>
       </c>
       <c r="F2">
-        <v>0.007599082179277888</v>
-      </c>
-      <c r="G2">
-        <v>0.2363310793492502</v>
-      </c>
-      <c r="H2">
-        <v>-8.026352053710584</v>
-      </c>
-      <c r="I2">
-        <v>1.611834517015938</v>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>EW</t>
-        </is>
-      </c>
-      <c r="K2">
-        <v>0.9102823215800314</v>
-      </c>
-      <c r="L2">
-        <v>0.005410543260007655</v>
-      </c>
-      <c r="M2">
-        <v>-7306.246381270323</v>
-      </c>
-      <c r="N2">
         <v>1467.867000750013</v>
-      </c>
-      <c r="O2">
-        <v>-29.10041817110508</v>
-      </c>
-      <c r="P2">
-        <v>5.846441703758192</v>
       </c>
     </row>
     <row r="3">
@@ -498,51 +416,22 @@
           <t>ASH</t>
         </is>
       </c>
-      <c r="B3">
-        <v>2.398160315374507</v>
-      </c>
-      <c r="C3" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>FS</t>
         </is>
       </c>
+      <c r="C3">
+        <v>-4.853362801476512</v>
+      </c>
       <c r="D3">
-        <v>-2.023785803793768</v>
+        <v>1.611834517015938</v>
       </c>
       <c r="E3">
-        <v>0.6721129136707557</v>
+        <v>-4417.930358398205</v>
       </c>
       <c r="F3">
-        <v>0.03950779448759779</v>
-      </c>
-      <c r="H3">
-        <v>-4.853362801476512</v>
-      </c>
-      <c r="I3">
-        <v>1.611834517015938</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>EW</t>
-        </is>
-      </c>
-      <c r="K3">
-        <v>0.9102823215800314</v>
-      </c>
-      <c r="L3">
-        <v>0.005410543260007655</v>
-      </c>
-      <c r="M3">
-        <v>-4417.930358398205</v>
-      </c>
-      <c r="N3">
         <v>1467.459432643888</v>
-      </c>
-      <c r="O3">
-        <v>-17.59639822847786</v>
-      </c>
-      <c r="P3">
-        <v>5.844818380138578</v>
       </c>
     </row>
     <row r="4">
@@ -551,54 +440,22 @@
           <t>LRE</t>
         </is>
       </c>
-      <c r="B4">
-        <v>2.529566360052562</v>
-      </c>
-      <c r="C4" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>BS</t>
         </is>
       </c>
+      <c r="C4">
+        <v>-6.709039740380804</v>
+      </c>
       <c r="D4">
-        <v>-2.652248957106386</v>
+        <v>1.628967108175865</v>
       </c>
       <c r="E4">
-        <v>0.6439708931541994</v>
+        <v>-6107.12027044653</v>
       </c>
       <c r="F4">
-        <v>0.01462924584275813</v>
-      </c>
-      <c r="G4">
-        <v>0.7201742245241556</v>
-      </c>
-      <c r="H4">
-        <v>-6.709039740380804</v>
-      </c>
-      <c r="I4">
-        <v>1.628967108175865</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>EW</t>
-        </is>
-      </c>
-      <c r="K4">
-        <v>0.9102823215800314</v>
-      </c>
-      <c r="L4">
-        <v>0.005410543260007655</v>
-      </c>
-      <c r="M4">
-        <v>-6107.12027044653</v>
-      </c>
-      <c r="N4">
         <v>1483.264202384465</v>
-      </c>
-      <c r="O4">
-        <v>-24.32435814740846</v>
-      </c>
-      <c r="P4">
-        <v>5.907767996747161</v>
       </c>
     </row>
     <row r="5">
@@ -607,51 +464,22 @@
           <t>LRE</t>
         </is>
       </c>
-      <c r="B5">
-        <v>2.529566360052562</v>
-      </c>
-      <c r="C5" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>FS</t>
         </is>
       </c>
+      <c r="C5">
+        <v>-5.823260412576844</v>
+      </c>
       <c r="D5">
-        <v>-2.302078531932976</v>
+        <v>1.628967108175865</v>
       </c>
       <c r="E5">
-        <v>0.6439708931541994</v>
+        <v>-5300.811007525541</v>
       </c>
       <c r="F5">
-        <v>0.02327515101231295</v>
-      </c>
-      <c r="H5">
-        <v>-5.823260412576844</v>
-      </c>
-      <c r="I5">
-        <v>1.628967108175865</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>EW</t>
-        </is>
-      </c>
-      <c r="K5">
-        <v>0.9102823215800314</v>
-      </c>
-      <c r="L5">
-        <v>0.005410543260007655</v>
-      </c>
-      <c r="M5">
-        <v>-5300.811007525541</v>
-      </c>
-      <c r="N5">
         <v>1483.154654094453</v>
-      </c>
-      <c r="O5">
-        <v>-21.11286821101835</v>
-      </c>
-      <c r="P5">
-        <v>5.907331671323282</v>
       </c>
     </row>
     <row r="6">
@@ -660,54 +488,22 @@
           <t>LRJ</t>
         </is>
       </c>
-      <c r="B6">
-        <v>2.266754270696452</v>
-      </c>
-      <c r="C6" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>BS</t>
         </is>
       </c>
+      <c r="C6">
+        <v>-5.87169357227485</v>
+      </c>
       <c r="D6">
-        <v>-2.590352932464441</v>
+        <v>1.490448284160137</v>
       </c>
       <c r="E6">
-        <v>0.6575253010120951</v>
+        <v>-3636.152786023719</v>
       </c>
       <c r="F6">
-        <v>0.01696578943374394</v>
-      </c>
-      <c r="G6">
-        <v>0.5623225497890948</v>
-      </c>
-      <c r="H6">
-        <v>-5.87169357227485</v>
-      </c>
-      <c r="I6">
-        <v>1.490448284160137</v>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>JW</t>
-        </is>
-      </c>
-      <c r="K6">
-        <v>0.6192681449169999</v>
-      </c>
-      <c r="L6">
-        <v>0.008516172438153556</v>
-      </c>
-      <c r="M6">
-        <v>-3636.152786023719</v>
-      </c>
-      <c r="N6">
         <v>924.3406858695798</v>
-      </c>
-      <c r="O6">
-        <v>-14.48261680287346</v>
-      </c>
-      <c r="P6">
-        <v>3.681603259414587</v>
       </c>
     </row>
     <row r="7">
@@ -716,51 +512,22 @@
           <t>LRJ</t>
         </is>
       </c>
-      <c r="B7">
-        <v>2.266754270696452</v>
-      </c>
-      <c r="C7" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>FS</t>
         </is>
       </c>
+      <c r="C7">
+        <v>-4.541750592417023</v>
+      </c>
       <c r="D7">
-        <v>-2.0036360584518</v>
+        <v>1.490448284160137</v>
       </c>
       <c r="E7">
-        <v>0.6575253010120951</v>
+        <v>-2812.561464041775</v>
       </c>
       <c r="F7">
-        <v>0.03813044306717106</v>
-      </c>
-      <c r="H7">
-        <v>-4.541750592417023</v>
-      </c>
-      <c r="I7">
-        <v>1.490448284160137</v>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>JW</t>
-        </is>
-      </c>
-      <c r="K7">
-        <v>0.6192681449169999</v>
-      </c>
-      <c r="L7">
-        <v>0.008516172438153556</v>
-      </c>
-      <c r="M7">
-        <v>-2812.561464041775</v>
-      </c>
-      <c r="N7">
         <v>923.7972079109103</v>
-      </c>
-      <c r="O7">
-        <v>-11.2022932795377</v>
-      </c>
-      <c r="P7">
-        <v>3.679438613570641</v>
       </c>
     </row>
     <row r="8">
@@ -769,54 +536,22 @@
           <t>LRW</t>
         </is>
       </c>
-      <c r="B8">
-        <v>2.529566360052562</v>
-      </c>
-      <c r="C8" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>BS</t>
         </is>
       </c>
+      <c r="C8">
+        <v>-5.841076613826704</v>
+      </c>
       <c r="D8">
-        <v>-2.309121715907596</v>
+        <v>1.454209853901234</v>
       </c>
       <c r="E8">
-        <v>0.574885038347449</v>
+        <v>-5317.028780561001</v>
       </c>
       <c r="F8">
-        <v>0.0003087071503610556</v>
-      </c>
-      <c r="G8">
-        <v>0.2490888123193706</v>
-      </c>
-      <c r="H8">
-        <v>-5.841076613826704</v>
-      </c>
-      <c r="I8">
-        <v>1.454209853901234</v>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>EW</t>
-        </is>
-      </c>
-      <c r="K8">
-        <v>0.9102823215800314</v>
-      </c>
-      <c r="L8">
-        <v>0.005410543260007655</v>
-      </c>
-      <c r="M8">
-        <v>-5317.028780561001</v>
-      </c>
-      <c r="N8">
         <v>1324.118722577073</v>
-      </c>
-      <c r="O8">
-        <v>-21.1774627993347</v>
-      </c>
-      <c r="P8">
-        <v>5.273899417621713</v>
       </c>
     </row>
     <row r="9">
@@ -825,51 +560,22 @@
           <t>LRW</t>
         </is>
       </c>
-      <c r="B9">
-        <v>2.529566360052562</v>
-      </c>
-      <c r="C9" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>FS</t>
         </is>
       </c>
+      <c r="C9">
+        <v>-8.252695879956793</v>
+      </c>
       <c r="D9">
-        <v>-3.262494319297206</v>
+        <v>1.454209853901234</v>
       </c>
       <c r="E9">
-        <v>0.574885038347449</v>
+        <v>-7512.28316490103</v>
       </c>
       <c r="F9">
-        <v>2.277256934190319E-06</v>
-      </c>
-      <c r="H9">
-        <v>-8.252695879956793</v>
-      </c>
-      <c r="I9">
-        <v>1.454209853901234</v>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>EW</t>
-        </is>
-      </c>
-      <c r="K9">
-        <v>0.9102823215800314</v>
-      </c>
-      <c r="L9">
-        <v>0.005410543260007655</v>
-      </c>
-      <c r="M9">
-        <v>-7512.28316490103</v>
-      </c>
-      <c r="N9">
         <v>1324.494386271162</v>
-      </c>
-      <c r="O9">
-        <v>-29.92105249540782</v>
-      </c>
-      <c r="P9">
-        <v>5.2753956675453</v>
       </c>
     </row>
     <row r="10">
@@ -878,54 +584,22 @@
           <t>MAG</t>
         </is>
       </c>
-      <c r="B10">
-        <v>2.299605781865966</v>
-      </c>
-      <c r="C10" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>BS</t>
         </is>
       </c>
+      <c r="C10">
+        <v>-7.38069329660139</v>
+      </c>
       <c r="D10">
-        <v>-3.209547199264947</v>
+        <v>7.017647292829975</v>
       </c>
       <c r="E10">
-        <v>3.051674051339206</v>
+        <v>-4570.628245987679</v>
       </c>
       <c r="F10">
-        <v>0.3522607045418362</v>
-      </c>
-      <c r="G10">
-        <v>0.8539754684526759</v>
-      </c>
-      <c r="H10">
-        <v>-7.38069329660139</v>
-      </c>
-      <c r="I10">
-        <v>7.017647292829975</v>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>JW</t>
-        </is>
-      </c>
-      <c r="K10">
-        <v>0.6192681449169999</v>
-      </c>
-      <c r="L10">
-        <v>0.008516172438153556</v>
-      </c>
-      <c r="M10">
-        <v>-4570.628245987679</v>
-      </c>
-      <c r="N10">
         <v>4346.259948278062</v>
-      </c>
-      <c r="O10">
-        <v>-18.20458636651948</v>
-      </c>
-      <c r="P10">
-        <v>17.31093852781169</v>
       </c>
     </row>
     <row r="11">
@@ -934,51 +608,22 @@
           <t>MAG</t>
         </is>
       </c>
-      <c r="B11">
-        <v>2.299605781865966</v>
-      </c>
-      <c r="C11" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>FS</t>
         </is>
       </c>
+      <c r="C11">
+        <v>-5.432935859652742</v>
+      </c>
       <c r="D11">
-        <v>-2.362550965254707</v>
+        <v>7.017647292829975</v>
       </c>
       <c r="E11">
-        <v>3.051674051339206</v>
+        <v>-3364.4441112602</v>
       </c>
       <c r="F11">
-        <v>0.4820366224397812</v>
-      </c>
-      <c r="H11">
-        <v>-5.432935859652742</v>
-      </c>
-      <c r="I11">
-        <v>7.017647292829975</v>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>JW</t>
-        </is>
-      </c>
-      <c r="K11">
-        <v>0.6192681449169999</v>
-      </c>
-      <c r="L11">
-        <v>0.008516172438153556</v>
-      </c>
-      <c r="M11">
-        <v>-3364.4441112602</v>
-      </c>
-      <c r="N11">
         <v>4346.051709970288</v>
-      </c>
-      <c r="O11">
-        <v>-13.40041458250973</v>
-      </c>
-      <c r="P11">
-        <v>17.31010912492555</v>
       </c>
     </row>
     <row r="12">
@@ -987,54 +632,22 @@
           <t>WD</t>
         </is>
       </c>
-      <c r="B12">
-        <v>2.398160315374507</v>
-      </c>
-      <c r="C12" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>BS</t>
         </is>
       </c>
+      <c r="C12">
+        <v>-4.832869201352993</v>
+      </c>
       <c r="D12">
-        <v>-2.015240253276509</v>
+        <v>2.121968187705888</v>
       </c>
       <c r="E12">
-        <v>0.8848316662159894</v>
+        <v>-2992.841944948371</v>
       </c>
       <c r="F12">
-        <v>0.02916216361765942</v>
-      </c>
-      <c r="G12">
-        <v>0.8166337376052223</v>
-      </c>
-      <c r="H12">
-        <v>-4.832869201352993</v>
-      </c>
-      <c r="I12">
-        <v>2.121968187705888</v>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>JW</t>
-        </is>
-      </c>
-      <c r="K12">
-        <v>0.6192681449169999</v>
-      </c>
-      <c r="L12">
-        <v>0.008516172438153556</v>
-      </c>
-      <c r="M12">
-        <v>-2992.841944948371</v>
-      </c>
-      <c r="N12">
         <v>1314.711687399592</v>
-      </c>
-      <c r="O12">
-        <v>-11.92034152328687</v>
-      </c>
-      <c r="P12">
-        <v>5.23643166152239</v>
       </c>
     </row>
     <row r="13">
@@ -1043,51 +656,22 @@
           <t>WD</t>
         </is>
       </c>
-      <c r="B13">
-        <v>2.398160315374507</v>
-      </c>
-      <c r="C13" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>FS</t>
         </is>
       </c>
+      <c r="C13">
+        <v>-4.131611250432497</v>
+      </c>
       <c r="D13">
-        <v>-1.722825294015962</v>
+        <v>2.121968187705888</v>
       </c>
       <c r="E13">
-        <v>0.8848316662159894</v>
+        <v>-2558.575234573539</v>
       </c>
       <c r="F13">
-        <v>0.05982545801930361</v>
-      </c>
-      <c r="H13">
-        <v>-4.131611250432497</v>
-      </c>
-      <c r="I13">
-        <v>2.121968187705888</v>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>JW</t>
-        </is>
-      </c>
-      <c r="K13">
-        <v>0.6192681449169999</v>
-      </c>
-      <c r="L13">
-        <v>0.008516172438153556</v>
-      </c>
-      <c r="M13">
-        <v>-2558.575234573539</v>
-      </c>
-      <c r="N13">
         <v>1314.538283069393</v>
-      </c>
-      <c r="O13">
-        <v>-10.19067868272159</v>
-      </c>
-      <c r="P13">
-        <v>5.235741000647006</v>
       </c>
     </row>
   </sheetData>
